--- a/Marketed_drugs.xlsx
+++ b/Marketed_drugs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\NGS\3_BUSINESS\Employee Folders\GCs\Andy Drackley\N1C\Gene Registry Updates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF6FE141-3229-4415-A826-2FF0B4B8F24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{571DA79E-2B1F-43E5-BABD-E3DE2417471F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
     <t>Strand</t>
   </si>
   <si>
-    <t>Condition/Indication</t>
+    <t>Condition/indication</t>
   </si>
   <si>
     <t>Generic Name</t>
